--- a/output/Data and Chart Outputs/indonesia_renewable_capacity.xlsx
+++ b/output/Data and Chart Outputs/indonesia_renewable_capacity.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Indonesia renewable installed capacity (ESDM EBTKE; renewables only) (to Apr/26)</a:t>
             </a:r>
           </a:p>
@@ -289,7 +290,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E87BA4"/>
+              <a:srgbClr val="6E4B2A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -317,7 +318,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="008300"/>
+              <a:srgbClr val="8A9A2B"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -345,7 +346,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="4A3AA7"/>
+              <a:srgbClr val="E87BA4"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -373,7 +374,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="E34948"/>
+              <a:srgbClr val="008300"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
